--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/valparaiso.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M362"/>
+  <dimension ref="A1:M365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>888.25</v>
+        <v>883.6799999999999</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>858.54</v>
+        <v>854.13</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2840.98</v>
+        <v>2826.38</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>767.5</v>
+        <v>763.55</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7287.47</v>
+        <v>7211.15</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1367.11</v>
+        <v>1352.79</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1238.85</v>
+        <v>1225.88</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7867.69</v>
+        <v>7824.68</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3304.48</v>
+        <v>3286.42</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6247.93</v>
+        <v>6178.32</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9185.870000000001</v>
+        <v>9083.530000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1486.06</v>
+        <v>1469.5</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1485.02</v>
+        <v>1476.89</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>773.9</v>
+        <v>769.66</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1960.19</v>
+        <v>1957.7</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2211.1</v>
+        <v>2218.99</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1837.8</v>
+        <v>1857.78</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3223.2</v>
+        <v>3258.25</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2789.65</v>
+        <v>2798.82</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9338.48</v>
+        <v>9499.68</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1049.34</v>
+        <v>1067.45</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>25156.97</v>
+        <v>25591.22</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1669.53</v>
+        <v>1681.09</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2935.27</v>
+        <v>2955.61</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5838.02</v>
+        <v>5878.47</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1075.83</v>
+        <v>1080.84</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1670.24</v>
+        <v>1678.02</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4184.72</v>
+        <v>4214.89</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1042.73</v>
+        <v>1050.24</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1182.42</v>
+        <v>1190.94</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1290.12</v>
+        <v>1299.42</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5677.08</v>
+        <v>5718.01</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5267.5</v>
+        <v>5258.16</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>71777.14</v>
+        <v>71649.83</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3107.19</v>
+        <v>3101.68</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>15160.84</v>
+        <v>15133.95</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2970.71</v>
+        <v>2965.44</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10782.28</v>
+        <v>10737.84</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>30920.85</v>
+        <v>30793.4</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5968.91</v>
+        <v>5944.31</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7030.8</v>
+        <v>7001.82</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1946</v>
+        <v>1937.98</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2431.16</v>
+        <v>2427.4</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>20728.51</v>
+        <v>20696.38</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>29520.52</v>
+        <v>29474.77</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13960.36</v>
+        <v>13938.72</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2459.69</v>
+        <v>2455.88</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3088.38</v>
+        <v>3110.18</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2572.27</v>
+        <v>2590.42</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3073.19</v>
+        <v>3034.15</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2000.48</v>
+        <v>1980.58</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>14104.75</v>
+        <v>14054.17</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1042.97</v>
+        <v>1039.23</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1374.2</v>
+        <v>1369.27</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8310.9</v>
+        <v>8281.1</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1894.02</v>
+        <v>1887.23</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>14300.3</v>
+        <v>14269.35</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>14136.12</v>
+        <v>14105.53</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1075.11</v>
+        <v>1070.6</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>23085.86</v>
+        <v>22989.07</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2369.58</v>
+        <v>2342.15</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3918.45</v>
+        <v>3915.3</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>7006.17</v>
+        <v>7000.54</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3467.31</v>
+        <v>3480.61</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3255.63</v>
+        <v>3268.12</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3087.67</v>
+        <v>3099.52</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>806.59</v>
+        <v>810.24</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>9536.459999999999</v>
+        <v>9579.68</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>871.12</v>
+        <v>875.0700000000001</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>19032.46</v>
+        <v>19118.7</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>927.78</v>
+        <v>931.99</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>12495.29</v>
+        <v>12528.43</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3623.18</v>
+        <v>3632.79</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3760.75</v>
+        <v>3755.47</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2448.42</v>
+        <v>2444.98</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3241.22</v>
+        <v>3236.67</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>4034.32</v>
+        <v>4039.49</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>793.28</v>
+        <v>798.74</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5447.93</v>
+        <v>5494.49</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1085.88</v>
+        <v>1095.16</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5244.61</v>
+        <v>5289.43</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>773.98</v>
+        <v>782.28</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>762.63</v>
+        <v>770.8099999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5943.26</v>
+        <v>6016.3</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1309.25</v>
+        <v>1326.07</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5956.38</v>
+        <v>6032.91</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>98716.06</v>
+        <v>99255.91</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>954.54</v>
+        <v>932.21</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2855.72</v>
+        <v>2814.57</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2694.5</v>
+        <v>2659.67</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1722.91</v>
+        <v>1700.64</v>
       </c>
     </row>
     <row r="93">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4359.86</v>
+        <v>4351.27</v>
       </c>
     </row>
     <row r="94">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1590.18</v>
+        <v>1587.04</v>
       </c>
     </row>
     <row r="95">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1109.68</v>
+        <v>1107.49</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2695.65</v>
+        <v>2690.34</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>14073.78</v>
+        <v>14064.16</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>988.33</v>
+        <v>984.9400000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4588.76</v>
+        <v>4573.01</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4788.07</v>
+        <v>4771.63</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3270.89</v>
+        <v>3259.67</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>7761.17</v>
+        <v>7734.54</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>5345.78</v>
+        <v>5317.55</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>4785.76</v>
+        <v>4760.48</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>954.01</v>
+        <v>948.97</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1069.08</v>
+        <v>1063.43</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1061.27</v>
+        <v>1054.62</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>848.1799999999999</v>
+        <v>842.86</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>832.8099999999999</v>
+        <v>827.59</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3364.93</v>
+        <v>3343.84</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>877.11</v>
+        <v>882.86</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1120.83</v>
+        <v>1137.9</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>10213.62</v>
+        <v>10461.99</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1130.17</v>
+        <v>1157.65</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>16911.03</v>
+        <v>17338.55</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>13498.76</v>
+        <v>13840.01</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>876.38</v>
+        <v>898.54</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>5195.68</v>
+        <v>5353.23</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>26001.76</v>
+        <v>26790.21</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1684.1</v>
+        <v>1735.16</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1386.92</v>
+        <v>1428.14</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1022.41</v>
+        <v>1052.8</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>18747.45</v>
+        <v>18680.7</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>11595.4</v>
+        <v>11508.62</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1166.87</v>
+        <v>1158.13</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>6520.83</v>
+        <v>6539.72</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2781.69</v>
+        <v>2789.74</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>6109</v>
+        <v>6126.7</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3399.49</v>
+        <v>3409.34</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1404.89</v>
+        <v>1412.15</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>818.42</v>
+        <v>814.97</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3901.76</v>
+        <v>3885.31</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2996.99</v>
+        <v>2984.35</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>14127.82</v>
+        <v>14068.25</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1291.56</v>
+        <v>1286.12</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>12517.7</v>
+        <v>12552.06</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1399.49</v>
+        <v>1412.22</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>5792.42</v>
+        <v>5845.11</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1065.41</v>
+        <v>1072.83</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>7573.37</v>
+        <v>7623.24</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2860.36</v>
+        <v>2879.2</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>23203.28</v>
+        <v>23356.09</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1096.29</v>
+        <v>1106.06</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>4092.07</v>
+        <v>4128.52</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>6094.81</v>
+        <v>6084.37</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>4236.56</v>
+        <v>4229.3</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>821.36</v>
+        <v>815.47</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1020.33</v>
+        <v>1013.02</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>18332.75</v>
+        <v>18305.78</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1465.25</v>
+        <v>1463.1</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3137.69</v>
+        <v>3120.6</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>8149.23</v>
+        <v>8104.86</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>6513.32</v>
+        <v>6477.85</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>39909.24</v>
+        <v>39691.91</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>4196.41</v>
+        <v>4173.55</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3599.27</v>
+        <v>3579.67</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1444.52</v>
+        <v>1436.01</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>14911.93</v>
+        <v>14989.13</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>15152.56</v>
+        <v>15231.01</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3838.56</v>
+        <v>3842.26</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1377.19</v>
+        <v>1417.19</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1396.65</v>
+        <v>1437.22</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>9890.950000000001</v>
+        <v>10053.97</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>5785.99</v>
+        <v>5881.35</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3256.58</v>
+        <v>3310.25</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>12402.21</v>
+        <v>12627.07</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>995.96</v>
+        <v>1014.01</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>8611.290000000001</v>
+        <v>8767.42</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1645.52</v>
+        <v>1671.3</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2999.94</v>
+        <v>2999.79</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>861.8200000000001</v>
+        <v>862.5700000000001</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1369.84</v>
+        <v>1371.02</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>873.64</v>
+        <v>877.25</v>
       </c>
     </row>
     <row r="174">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>72731.92</v>
+        <v>72531.3</v>
       </c>
     </row>
     <row r="175">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1453.55</v>
+        <v>1449.54</v>
       </c>
     </row>
     <row r="176">
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>7822.38</v>
+        <v>7732.07</v>
       </c>
     </row>
     <row r="177">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>5476.28</v>
+        <v>5413.06</v>
       </c>
     </row>
     <row r="178">
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>59421.97</v>
+        <v>58735.99</v>
       </c>
     </row>
     <row r="179">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2424.07</v>
+        <v>2396.08</v>
       </c>
     </row>
     <row r="180">
@@ -11435,13 +11435,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7913.16</v>
+        <v>7821.81</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2799-329-CM26</t>
+          <t>2799-328-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11496,13 +11496,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2865.81</v>
+        <v>2790.8</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2799-328-CM26</t>
+          <t>2799-329-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2833.05</v>
+        <v>2823.06</v>
       </c>
     </row>
     <row r="183">
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>893.39</v>
+        <v>880.0599999999999</v>
       </c>
     </row>
     <row r="184">
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>979.59</v>
+        <v>973.97</v>
       </c>
     </row>
     <row r="185">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>8104.8</v>
+        <v>8069.88</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2479.54</v>
+        <v>2443.67</v>
       </c>
     </row>
     <row r="187">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2420.06</v>
+        <v>2385.05</v>
       </c>
     </row>
     <row r="188">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1773.39</v>
+        <v>1747.73</v>
       </c>
     </row>
     <row r="189">
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>11110.76</v>
+        <v>10950.02</v>
       </c>
     </row>
     <row r="190">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>779.54</v>
+        <v>762.76</v>
       </c>
     </row>
     <row r="191">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1631.9</v>
+        <v>1596.79</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>6502.77</v>
+        <v>6295.42</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>3641.75</v>
+        <v>3525.63</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2324.3</v>
+        <v>2250.18</v>
       </c>
     </row>
     <row r="195">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>881.35</v>
+        <v>863.97</v>
       </c>
     </row>
     <row r="196">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>16494.79</v>
+        <v>16060.43</v>
       </c>
     </row>
     <row r="197">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>5086.9</v>
+        <v>4952.95</v>
       </c>
     </row>
     <row r="198">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1338.57</v>
+        <v>1303.32</v>
       </c>
     </row>
     <row r="199">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2004.66</v>
+        <v>1951.87</v>
       </c>
     </row>
     <row r="200">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>5008.43</v>
+        <v>4876.55</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2018.97</v>
+        <v>1964.91</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2666.67</v>
+        <v>2674.44</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>7496.11</v>
+        <v>7559.73</v>
       </c>
     </row>
     <row r="204">
@@ -12899,13 +12899,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>902.02</v>
+        <v>909.6799999999999</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2737-203-CM26</t>
+          <t>4548-237-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12925,17 +12925,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>99.590.760-7</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12960,13 +12960,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1876.67</v>
+        <v>3360.15</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3086-368-CM26</t>
+          <t>2737-203-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.102.005-8</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13021,13 +13021,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3801.06</v>
+        <v>1892.6</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>4548-237-CM26</t>
+          <t>3086-368-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13047,17 +13047,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>61.102.005-8</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>CENTRO DE ABASTECIMIENTO (V)</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13067,12 +13067,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
+          <t>84.634.200-1</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>3331.87</v>
+        <v>3833.32</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>7768.98</v>
+        <v>7755.99</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3082.07</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2895.54</v>
+        <v>2931.18</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>779.96</v>
+        <v>789.5599999999999</v>
       </c>
     </row>
     <row r="212">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1669.91</v>
+        <v>1692.14</v>
       </c>
     </row>
     <row r="213">
@@ -13448,13 +13448,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>6417.02</v>
+        <v>6502.45</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2799-413-CM26</t>
+          <t>4964-26-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13509,13 +13509,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1991.21</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4964-26-CM26</t>
+          <t>2799-413-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13540,12 +13540,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2775.78</v>
+        <v>2017.19</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>14375.9</v>
+        <v>14729.69</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3469.59</v>
+        <v>3535.21</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>994.99</v>
+        <v>1013.81</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3584.29</v>
+        <v>3652.08</v>
       </c>
     </row>
     <row r="220">
@@ -13875,13 +13875,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3753.08</v>
+        <v>3795.76</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1113403-63-CM26</t>
+          <t>2427-334-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13901,17 +13901,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>62.000.650-5</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE GABRIELA MISTRAL</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13921,12 +13921,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13936,13 +13936,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>5660.92</v>
+        <v>5252.85</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3820-348-CM26</t>
+          <t>2427-335-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13967,12 +13967,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13997,13 +13997,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>989.8099999999999</v>
+        <v>11261.76</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2427-334-CM26</t>
+          <t>1113403-63-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14023,17 +14023,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>62.000.650-5</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE GABRIELA MISTRAL</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14058,13 +14058,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>5205.95</v>
+        <v>5711.92</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2427-335-CM26</t>
+          <t>3820-348-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14104,12 +14104,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>11161.22</v>
+        <v>998.72</v>
       </c>
     </row>
     <row r="225">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2175.17</v>
+        <v>2189.08</v>
       </c>
     </row>
     <row r="226">
@@ -14241,13 +14241,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>3281.86</v>
+        <v>3292.18</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2428-395-CM26</t>
+          <t>1173462-8-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14272,12 +14272,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.969.100-8</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>11798.92</v>
+        <v>6250.69</v>
       </c>
     </row>
     <row r="228">
@@ -14363,13 +14363,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3077.1</v>
+        <v>3089.86</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1173462-8-CM26</t>
+          <t>2428-395-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14394,12 +14394,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.969.100-8</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14409,12 +14409,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>6224.89</v>
+        <v>11847.82</v>
       </c>
     </row>
     <row r="230">
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>3424.45</v>
+        <v>3431.55</v>
       </c>
     </row>
     <row r="231">
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>5251.24</v>
+        <v>5262.12</v>
       </c>
     </row>
     <row r="232">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1479.83</v>
+        <v>1473.47</v>
       </c>
     </row>
     <row r="233">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1110.82</v>
+        <v>1106.04</v>
       </c>
     </row>
     <row r="234">
@@ -14729,13 +14729,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>8163.82</v>
+        <v>8114.89</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5554-13-CM26</t>
+          <t>576181-83-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14755,17 +14755,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.979.760-4</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>BASE INFANTERIA DE MARINA CONCON</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14775,12 +14775,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.724.952-7</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -14790,13 +14790,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1702.19</v>
+        <v>5217.89</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>576181-83-CM26</t>
+          <t>5554-13-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14816,17 +14816,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.979.760-4</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA CONCON</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14836,12 +14836,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>5262.78</v>
+        <v>1687.67</v>
       </c>
     </row>
     <row r="237">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1133.38</v>
+        <v>1139.48</v>
       </c>
     </row>
     <row r="238">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>21642.47</v>
+        <v>21759.01</v>
       </c>
     </row>
     <row r="239">
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>34020.14</v>
+        <v>34203.34</v>
       </c>
     </row>
     <row r="240">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>4983.95</v>
+        <v>5039.69</v>
       </c>
     </row>
     <row r="241">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>11175.96</v>
+        <v>11260.61</v>
       </c>
     </row>
     <row r="242">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>3549.32</v>
+        <v>3562.77</v>
       </c>
     </row>
     <row r="243">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1020.27</v>
+        <v>1024.13</v>
       </c>
     </row>
     <row r="244">
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>14261.8</v>
+        <v>14315.83</v>
       </c>
     </row>
     <row r="245">
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1447.55</v>
+        <v>1443.89</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3191-2247-CM26</t>
+          <t>1431841-370-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>DISTRIBUIDORA NACIONAL DE ARTICULOS DE SEGURIDAD LIMITADA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
+          <t>78.339.640-8</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15461,13 +15461,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>3102.59</v>
+        <v>812.0700000000001</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>3882-177-CM26</t>
+          <t>3191-2247-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.724.952-7</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15522,13 +15522,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>6907.52</v>
+        <v>3132.07</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1431841-370-CM26</t>
+          <t>3882-177-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15553,12 +15553,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15568,12 +15568,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NACIONAL DE ARTICULOS DE SEGURIDAD LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>78.339.640-8</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15583,7 +15583,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>804.4299999999999</v>
+        <v>6973.14</v>
       </c>
     </row>
     <row r="249">
@@ -15644,7 +15644,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3909.64</v>
+        <v>3938.77</v>
       </c>
     </row>
     <row r="250">
@@ -15705,13 +15705,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>11235.78</v>
+        <v>11123.73</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5196-374-CM26</t>
+          <t>1431841-440-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15731,17 +15731,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.978.670-K</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15751,12 +15751,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -15766,13 +15766,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2563.52</v>
+        <v>20235.63</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1431841-440-CM26</t>
+          <t>5196-374-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15792,17 +15792,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>61.978.670-K</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>IIª Brigada Aérea</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15812,12 +15812,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>20324.72</v>
+        <v>2552.29</v>
       </c>
     </row>
     <row r="253">
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1205.14</v>
+        <v>1192.03</v>
       </c>
     </row>
     <row r="254">
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>7414.47</v>
+        <v>7333.82</v>
       </c>
     </row>
     <row r="255">
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1050.22</v>
+        <v>1038.8</v>
       </c>
     </row>
     <row r="256">
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2179.9</v>
+        <v>2156.19</v>
       </c>
     </row>
     <row r="257">
@@ -16132,13 +16132,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1327.09</v>
+        <v>1324.08</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2696-44-CM26</t>
+          <t>707419-53-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16163,12 +16163,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16178,12 +16178,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16193,13 +16193,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1530.16</v>
+        <v>15654.94</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>707419-53-CM26</t>
+          <t>2696-44-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16254,7 +16254,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>15693.7</v>
+        <v>1526.39</v>
       </c>
     </row>
     <row r="260">
@@ -16315,7 +16315,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>3779.32</v>
+        <v>3791.86</v>
       </c>
     </row>
     <row r="261">
@@ -16376,13 +16376,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2784.69</v>
+        <v>2793.93</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>3047-230-CM26</t>
+          <t>1173462-10-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>61.969.100-8</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1256.59</v>
+        <v>827.4299999999999</v>
       </c>
     </row>
     <row r="263">
@@ -16498,13 +16498,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>9312.84</v>
+        <v>9342.48</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1173462-10-CM26</t>
+          <t>3047-230-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16529,12 +16529,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.969.100-8</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>Academia Politécnica Naval</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16544,12 +16544,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>824.8</v>
+        <v>1260.59</v>
       </c>
     </row>
     <row r="265">
@@ -16620,13 +16620,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1030.73</v>
+        <v>1036.21</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3238-35-CM26</t>
+          <t>1422051-182-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16651,12 +16651,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.950.600-6</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DIRECCION DE INTERESES MARITIMOS Y MEDIO AMBIENTE</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16666,12 +16666,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16681,13 +16681,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1139.2</v>
+        <v>911.23</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1953-979-CM26</t>
+          <t>2424-690-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16712,12 +16712,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16727,12 +16727,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -16742,13 +16742,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>800.3200000000001</v>
+        <v>20510.05</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1422051-182-CM26</t>
+          <t>3238-35-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16773,12 +16773,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>61.950.600-6</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>DIRECCION DE INTERESES MARITIMOS Y MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16788,12 +16788,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -16803,13 +16803,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>898.38</v>
+        <v>1155.51</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2424-690-CM26</t>
+          <t>1953-979-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16834,12 +16834,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16849,12 +16849,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>20220.71</v>
+        <v>811.77</v>
       </c>
     </row>
     <row r="270">
@@ -16925,13 +16925,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>8358.91</v>
+        <v>8478.52</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>4301-358-CM26</t>
+          <t>4077-78-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16951,17 +16951,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>V ZONA CARABINEROS VALPARAISO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -16971,12 +16971,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -16986,13 +16986,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>4412.35</v>
+        <v>7111.52</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>4077-78-CM26</t>
+          <t>4301-358-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17012,17 +17012,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17032,12 +17032,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>7029.06</v>
+        <v>4464.11</v>
       </c>
     </row>
     <row r="273">
@@ -17108,13 +17108,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>9879.52</v>
+        <v>10046.6</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>701-307-CM26</t>
+          <t>2799-564-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17139,12 +17139,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17154,12 +17154,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17169,13 +17169,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1318.57</v>
+        <v>1743.9</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2799-564-CM26</t>
+          <t>701-307-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17200,12 +17200,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17215,12 +17215,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17230,7 +17230,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1773.87</v>
+        <v>1296.29</v>
       </c>
     </row>
     <row r="276">
@@ -17291,7 +17291,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>8997.719999999999</v>
+        <v>8870.02</v>
       </c>
     </row>
     <row r="277">
@@ -17352,7 +17352,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1199.64</v>
+        <v>1182.61</v>
       </c>
     </row>
     <row r="278">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>4424.5</v>
+        <v>4363.71</v>
       </c>
     </row>
     <row r="279">
@@ -17474,13 +17474,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>919.89</v>
+        <v>914.1799999999999</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1422051-213-CM26</t>
+          <t>799512-626-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17505,12 +17505,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17520,12 +17520,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K280" t="inlineStr"/>
@@ -17535,13 +17535,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1756.24</v>
+        <v>2188.52</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1422051-212-CM26</t>
+          <t>3820-521-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17561,17 +17561,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17581,12 +17581,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>IMPORTADORA DOWNLIGHT SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.708.540-9</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -17596,13 +17596,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>4443.24</v>
+        <v>17771.47</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>3820-521-CM26</t>
+          <t>2427-532-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17622,17 +17622,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>IMPORTADORA DOWNLIGHT SPA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>77.708.540-9</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -17657,13 +17657,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>17691.12</v>
+        <v>962.1900000000001</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>799512-626-CM26</t>
+          <t>1422051-212-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17688,12 +17688,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17703,12 +17703,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -17718,13 +17718,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2178.63</v>
+        <v>4463.42</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2427-532-CM26</t>
+          <t>1422051-213-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17749,12 +17749,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17764,12 +17764,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>957.84</v>
+        <v>1764.21</v>
       </c>
     </row>
     <row r="285">
@@ -17840,13 +17840,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>1947.68</v>
+        <v>1976.68</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5509-35-CM26</t>
+          <t>2698-146-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17871,12 +17871,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17886,12 +17886,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -17901,13 +17901,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2102.48</v>
+        <v>3143.43</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3820-522-CM26</t>
+          <t>1099899-107-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17927,17 +17927,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -17947,12 +17947,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K287" t="inlineStr"/>
@@ -17962,13 +17962,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>935.71</v>
+        <v>1065.7</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1099899-107-CM26</t>
+          <t>5509-35-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17988,17 +17988,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18008,12 +18008,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K288" t="inlineStr"/>
@@ -18023,13 +18023,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1045.82</v>
+        <v>2142.45</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2698-146-CM26</t>
+          <t>3820-522-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18054,12 +18054,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>3084.78</v>
+        <v>953.5</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1422051-217-CM26</t>
+          <t>2755-229-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18115,12 +18115,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18130,12 +18130,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18145,13 +18145,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1946.29</v>
+        <v>9548.65</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>903556-37-CM26</t>
+          <t>760-192-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18171,17 +18171,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18191,12 +18191,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -18206,13 +18206,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>7999.72</v>
+        <v>820.3</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2799-586-CM26</t>
+          <t>903556-37-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18237,12 +18237,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18252,12 +18252,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18267,13 +18267,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>26916.88</v>
+        <v>8180.14</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2755-229-CM26</t>
+          <t>2799-586-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18293,17 +18293,17 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18313,12 +18313,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -18328,13 +18328,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>9338.049999999999</v>
+        <v>27523.93</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>760-192-CM26</t>
+          <t>1422051-217-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18359,12 +18359,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18374,12 +18374,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>802.21</v>
+        <v>1990.18</v>
       </c>
     </row>
     <row r="295">
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>3701.31</v>
+        <v>3726.87</v>
       </c>
     </row>
     <row r="296">
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1107.25</v>
+        <v>1114.9</v>
       </c>
     </row>
     <row r="297">
@@ -18572,7 +18572,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>4492.26</v>
+        <v>4506.15</v>
       </c>
     </row>
     <row r="298">
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>1019.19</v>
+        <v>1016.49</v>
       </c>
     </row>
     <row r="299">
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2618.48</v>
+        <v>2583.61</v>
       </c>
     </row>
     <row r="300">
@@ -18755,13 +18755,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>4470.85</v>
+        <v>4383.34</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>836-105-CM26</t>
+          <t>4964-60-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18781,17 +18781,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18816,13 +18816,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>3110.08</v>
+        <v>1070.65</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2698-161-CM26</t>
+          <t>2176-315-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18847,12 +18847,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18862,12 +18862,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
@@ -18877,13 +18877,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>8778.809999999999</v>
+        <v>3903.64</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1943-205-CM26</t>
+          <t>2920-121-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18903,17 +18903,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.252.300-8</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18923,12 +18923,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEGURIDAD INDUSTRIAL SPA </t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>76.756.768-5</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K303" t="inlineStr"/>
@@ -18938,13 +18938,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>5137.35</v>
+        <v>1394.24</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1231-64-CM26</t>
+          <t>836-105-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -18964,17 +18964,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>60.804.008-0</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE VALPARAISO</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -18984,12 +18984,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -18999,13 +18999,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>798.02</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2176-315-CM26</t>
+          <t>1231-64-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19025,17 +19025,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.804.008-0</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE VALPARAISO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19045,12 +19045,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K305" t="inlineStr"/>
@@ -19060,13 +19060,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3962.34</v>
+        <v>786.2</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>4964-60-CM26</t>
+          <t>1943-205-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19091,12 +19091,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19106,12 +19106,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t xml:space="preserve">SEGURIDAD INDUSTRIAL SPA </t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.756.768-5</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
@@ -19121,13 +19121,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1086.75</v>
+        <v>5061.23</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2920-121-CM26</t>
+          <t>2698-161-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19152,12 +19152,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19167,12 +19167,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1415.21</v>
+        <v>8648.74</v>
       </c>
     </row>
     <row r="308">
@@ -19243,7 +19243,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1028.92</v>
+        <v>1007.78</v>
       </c>
     </row>
     <row r="309">
@@ -19304,13 +19304,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>4280.08</v>
+        <v>4320.74</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2698-167-CM26</t>
+          <t>377-274-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19330,17 +19330,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19350,12 +19350,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19365,13 +19365,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>986.05</v>
+        <v>1784.45</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>377-274-CM26</t>
+          <t>2698-167-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19391,17 +19391,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19411,12 +19411,12 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
@@ -19426,13 +19426,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1777.52</v>
+        <v>989.9</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2428-695-CM26</t>
+          <t>1171085-28-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19457,12 +19457,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19472,12 +19472,12 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K312" t="inlineStr"/>
@@ -19487,13 +19487,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>931.17</v>
+        <v>986.8200000000001</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1953-1201-CM26</t>
+          <t>2428-695-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -19513,17 +19513,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19533,12 +19533,12 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K313" t="inlineStr"/>
@@ -19548,13 +19548,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2431.35</v>
+        <v>940.5</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1171085-28-CM26</t>
+          <t>1953-1201-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19574,17 +19574,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19594,12 +19594,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -19609,13 +19609,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>977.04</v>
+        <v>2455.69</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1704-3640-CM26</t>
+          <t>3223-118-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -19635,17 +19635,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.102.019-8</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19655,12 +19655,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.724.952-7</t>
         </is>
       </c>
       <c r="K315" t="inlineStr"/>
@@ -19670,13 +19670,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>778.14</v>
+        <v>1526.9</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3223-118-CM26</t>
+          <t>2698-169-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19696,17 +19696,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.102.019-8</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19716,12 +19716,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -19731,13 +19731,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1519.16</v>
+        <v>4542.43</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2698-169-CM26</t>
+          <t>1704-3640-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19762,12 +19762,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -19792,13 +19792,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>4519.4</v>
+        <v>782.1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>4548-429-CM26</t>
+          <t>2698-172-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19823,12 +19823,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -19838,12 +19838,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K318" t="inlineStr"/>
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>12484.4</v>
+        <v>5077.72</v>
       </c>
     </row>
     <row r="319">
@@ -19914,13 +19914,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>14881.74</v>
+        <v>14806.36</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2698-172-CM26</t>
+          <t>4548-429-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -19945,12 +19945,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -19960,12 +19960,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K320" t="inlineStr"/>
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>5103.57</v>
+        <v>12421.16</v>
       </c>
     </row>
     <row r="321">
@@ -20036,7 +20036,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>14509.42</v>
+        <v>14540.35</v>
       </c>
     </row>
     <row r="322">
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>3433.14</v>
+        <v>3440.46</v>
       </c>
     </row>
     <row r="323">
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>791.4</v>
+        <v>796.5599999999999</v>
       </c>
     </row>
     <row r="324">
@@ -20219,7 +20219,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1695.33</v>
+        <v>1699.21</v>
       </c>
     </row>
     <row r="325">
@@ -20280,13 +20280,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>4476.56</v>
+        <v>4486.82</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2428-766-CM26</t>
+          <t>4077-106-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20311,12 +20311,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>V ZONA CARABINEROS VALPARAISO</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K326" t="inlineStr"/>
@@ -20341,13 +20341,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>7955.23</v>
+        <v>9678.74</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>4077-106-CM26</t>
+          <t>760-231-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20367,17 +20367,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K327" t="inlineStr"/>
@@ -20402,13 +20402,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>9614.379999999999</v>
+        <v>1405.18</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>760-231-CM26</t>
+          <t>2428-766-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20428,17 +20428,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K328" t="inlineStr"/>
@@ -20463,13 +20463,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1395.83</v>
+        <v>8008.48</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>4844-54-CM26</t>
+          <t>1431841-788-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -20494,12 +20494,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K329" t="inlineStr"/>
@@ -20524,13 +20524,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>18584.69</v>
+        <v>3258.6</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>3882-281-CM26</t>
+          <t>2698-177-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -20550,17 +20550,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20570,12 +20570,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K330" t="inlineStr"/>
@@ -20585,13 +20585,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2086.18</v>
+        <v>5755.17</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2698-177-CM26</t>
+          <t>3882-281-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -20611,17 +20611,17 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20631,12 +20631,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K331" t="inlineStr"/>
@@ -20646,13 +20646,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>5715.18</v>
+        <v>2100.78</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1431841-788-CM26</t>
+          <t>4844-54-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -20677,12 +20677,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20692,12 +20692,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>3235.95</v>
+        <v>18714.75</v>
       </c>
     </row>
     <row r="333">
@@ -20768,7 +20768,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>986.05</v>
+        <v>992.95</v>
       </c>
     </row>
     <row r="334">
@@ -20829,13 +20829,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>856.3099999999999</v>
+        <v>862.3</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>4301-487-CM26</t>
+          <t>568658-1093-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -20860,12 +20860,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20875,12 +20875,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K335" t="inlineStr"/>
@@ -20890,13 +20890,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3604.13</v>
+        <v>7108.38</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>568658-1093-CM26</t>
+          <t>2737-446-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -20916,17 +20916,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -20936,12 +20936,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K336" t="inlineStr"/>
@@ -20951,13 +20951,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>7123.88</v>
+        <v>2447.73</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2737-446-CM26</t>
+          <t>4301-487-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -20977,17 +20977,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -20997,12 +20997,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K337" t="inlineStr"/>
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2453.06</v>
+        <v>3596.29</v>
       </c>
     </row>
     <row r="338">
@@ -21073,7 +21073,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1302.19</v>
+        <v>1299.58</v>
       </c>
     </row>
     <row r="339">
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>5763.19</v>
+        <v>5751.63</v>
       </c>
     </row>
     <row r="340">
@@ -21195,7 +21195,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>3722.35</v>
+        <v>3700.81</v>
       </c>
     </row>
     <row r="341">
@@ -21256,13 +21256,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>11647.51</v>
+        <v>11459.55</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>568658-1133-CM26</t>
+          <t>1422051-247-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21287,12 +21287,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21302,12 +21302,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>J RAVERA Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>80.780.200-3</t>
         </is>
       </c>
       <c r="K342" t="inlineStr"/>
@@ -21317,13 +21317,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>8428.440000000001</v>
+        <v>9256.07</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1422051-247-CM26</t>
+          <t>1422051-248-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21363,12 +21363,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>J RAVERA Y COMPANIA LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>80.780.200-3</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K343" t="inlineStr"/>
@@ -21378,13 +21378,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>9406.9</v>
+        <v>2355.45</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1422051-248-CM26</t>
+          <t>1422051-249-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21439,13 +21439,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2393.83</v>
+        <v>761.63</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1422051-249-CM26</t>
+          <t>568658-1133-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21470,12 +21470,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21485,12 +21485,12 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K345" t="inlineStr"/>
@@ -21500,7 +21500,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>774.04</v>
+        <v>8293.299999999999</v>
       </c>
     </row>
     <row r="346">
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>6616.9</v>
+        <v>6510.81</v>
       </c>
     </row>
     <row r="347">
@@ -21622,7 +21622,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>857.27</v>
+        <v>843.53</v>
       </c>
     </row>
     <row r="348">
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>5139.43</v>
+        <v>5079.63</v>
       </c>
     </row>
     <row r="349">
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1220.72</v>
+        <v>1206.51</v>
       </c>
     </row>
     <row r="350">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>961.72</v>
+        <v>950.53</v>
       </c>
     </row>
     <row r="351">
@@ -21866,7 +21866,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>1748.63</v>
+        <v>1728.28</v>
       </c>
     </row>
     <row r="352">
@@ -21927,13 +21927,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1315.31</v>
+        <v>1308.01</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2920-161-CM26</t>
+          <t>1134432-543-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -21958,12 +21958,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -21973,12 +21973,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>11.647.874-9</t>
         </is>
       </c>
       <c r="K353" t="inlineStr"/>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1816.4</v>
+        <v>31708.23</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2427-660-CM26</t>
+          <t>2513-29-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22019,12 +22019,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22034,12 +22034,12 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K354" t="inlineStr"/>
@@ -22049,13 +22049,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>4368.05</v>
+        <v>1153.18</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2755-320-CM26</t>
+          <t>2427-660-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22080,12 +22080,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>11.647.874-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K355" t="inlineStr"/>
@@ -22110,13 +22110,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1752.57</v>
+        <v>4346.57</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1134432-543-CM26</t>
+          <t>2920-161-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22141,12 +22141,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.252.300-8</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -22156,12 +22156,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>11.647.874-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K356" t="inlineStr"/>
@@ -22171,13 +22171,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>31864.91</v>
+        <v>1807.47</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2513-29-CM26</t>
+          <t>2755-320-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22202,12 +22202,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -22217,12 +22217,12 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>11.647.874-9</t>
         </is>
       </c>
       <c r="K357" t="inlineStr"/>
@@ -22232,13 +22232,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1158.87</v>
+        <v>1743.95</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1028-233-CM26</t>
+          <t>3275-7159-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22263,12 +22263,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -22278,12 +22278,12 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K358" t="inlineStr"/>
@@ -22293,13 +22293,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>12565.83</v>
+        <v>1889.62</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3275-7161-CM26</t>
+          <t>2958-50-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22324,12 +22324,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.102.011-2</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Comandancia General del Cuerpo I.M.</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22339,12 +22339,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K359" t="inlineStr"/>
@@ -22354,13 +22354,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1838.3</v>
+        <v>40489.72</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>3275-7159-CM26</t>
+          <t>1028-233-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22385,12 +22385,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22400,12 +22400,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K360" t="inlineStr"/>
@@ -22415,13 +22415,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1877.05</v>
+        <v>12649.94</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2958-50-CM26</t>
+          <t>3275-7161-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -22446,12 +22446,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.102.011-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Comandancia General del Cuerpo I.M.</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -22461,12 +22461,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K361" t="inlineStr"/>
@@ -22476,7 +22476,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>40220.51</v>
+        <v>1850.6</v>
       </c>
     </row>
     <row r="362">
@@ -22537,7 +22537,190 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>30982.82</v>
+        <v>31190.2</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1431841-925-CM26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>69.254.800-0</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>898.95</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1431841-974-CM26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>69.254.800-0</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>19689.56</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>4548-528-CM26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>69.060.700-k</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>99.590.760-7</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>2286.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/valparaiso.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/valparaiso.xlsx
@@ -745,7 +745,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +993,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1180,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1367,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1737,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1802,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2843,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3213,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3278,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3404,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3469,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4022,11 @@
           <t>77.094.046-K</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4392,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4518,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4705,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4770,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5018,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6181,11 @@
           <t>77.163.842-2</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6673,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6799,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +6986,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7112,11 @@
           <t>10.020.938-1</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7543,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7608,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7673,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7738,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7864,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +7990,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8055,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8120,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8246,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8555,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8620,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9356,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9482,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9608,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9734,11 @@
           <t>77.103.803-4</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9799,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +9986,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10295,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10360,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10425,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10490,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +10921,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +10986,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11112,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11299,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11730,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11795,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +11921,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12047,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12295,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12360,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12730,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12795,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +12860,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +12925,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +12990,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13177,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13364,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13490,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13555,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13681,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +13990,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14787,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +14913,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15100,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15409,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15718,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15783,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15848,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +15974,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16100,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16348,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16657,11 @@
           <t>10.020.938-1</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +16783,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +16909,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17157,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17466,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +17714,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18023,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18271,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18397,11 @@
           <t>77.094.046-K</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18523,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +18893,11 @@
           <t>10.020.938-1</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +18958,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19084,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19149,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19214,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19462,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19527,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19653,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +19718,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +19844,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +19909,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20279,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20588,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +20775,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +20840,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +20905,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21031,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21157,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21283,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21409,11 @@
           <t>10.020.938-1</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21474,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21539,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21604,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +21730,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +21795,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22043,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22230,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22356,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22421,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22486,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +22612,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +22677,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +22803,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23051,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23116,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23181,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23307,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23372,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23437,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +23807,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +23994,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24059,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24185,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +24555,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +24681,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +24868,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25238,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +25608,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +25673,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +25738,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +25986,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26051,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26177,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +26486,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +26551,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +26677,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27108,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27295,11 @@
           <t>10.020.938-1</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +27482,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +27608,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +27738,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +27925,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27772,7 +28356,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +28421,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +28547,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +28612,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +28860,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +29047,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +29478,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28992,7 +29604,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +29852,11 @@
           <t>10.020.938-1</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +30344,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +30531,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +31023,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +31332,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +31397,11 @@
           <t>77.094.046-K</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +31889,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +31954,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +32019,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +32389,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +32881,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32473,7 +33133,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33083,7 +33747,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33205,7 +33873,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33327,7 +33999,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33388,7 +34064,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33510,7 +34190,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33571,7 +34255,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33632,7 +34320,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33876,7 +34568,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34059,7 +34755,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34120,7 +34820,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34181,7 +34885,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34486,7 +35194,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34669,7 +35381,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34913,7 +35629,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34974,7 +35694,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35035,7 +35759,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35279,7 +36007,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36011,7 +36743,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36072,7 +36808,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36133,7 +36873,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36194,7 +36938,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36316,7 +37064,11 @@
           <t>77.714.558-4</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36377,7 +37129,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36621,7 +37377,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36682,7 +37442,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36743,7 +37507,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36865,7 +37633,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37109,7 +37881,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37170,7 +37946,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37231,7 +38011,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37292,7 +38076,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37353,7 +38141,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38756,7 +39548,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39061,7 +39857,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39122,7 +39922,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39549,7 +40353,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39976,7 +40784,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40342,7 +41154,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40403,7 +41219,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40464,7 +41284,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40708,7 +41532,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40891,7 +41719,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40952,7 +41784,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41013,7 +41849,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41074,7 +41914,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41196,7 +42040,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41257,7 +42105,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41562,7 +42414,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41623,7 +42479,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41684,7 +42544,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41745,7 +42609,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41867,7 +42735,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42050,7 +42922,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42111,7 +42987,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42294,7 +43174,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42538,7 +43422,11 @@
           <t>77.094.046-K</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42599,7 +43487,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42660,7 +43552,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42721,7 +43617,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42782,7 +43682,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42843,7 +43747,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42965,7 +43873,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43209,7 +44121,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43575,7 +44491,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43758,7 +44678,11 @@
           <t>77.094.046-K</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43819,7 +44743,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43880,7 +44808,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43941,7 +44873,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44063,7 +44999,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44246,7 +45186,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44368,7 +45312,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45222,7 +46170,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45588,7 +46540,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45771,7 +46727,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46076,7 +47036,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46137,7 +47101,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46259,7 +47227,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46320,7 +47292,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46442,7 +47418,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46503,7 +47483,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46564,7 +47548,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46625,7 +47613,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46686,7 +47678,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/valparaiso.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/valparaiso.xlsx
@@ -2172,7 +2172,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2416,7 +2420,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6059,7 +6067,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8807,7 +8819,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9112,7 +9128,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9173,7 +9193,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9234,7 +9258,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15287,7 +15315,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16287,7 +16319,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16535,7 +16571,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18088,7 +18128,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20466,7 +20510,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21096,7 +21144,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21921,7 +21973,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29356,7 +29412,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31767,7 +31827,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33259,7 +33323,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33320,7 +33388,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33686,7 +33758,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38267,7 +38343,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38938,7 +39018,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40170,7 +40254,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40601,7 +40689,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40849,7 +40941,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44060,7 +44156,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/valparaiso.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M800"/>
+  <dimension ref="A1:M801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -31909,7 +31909,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2594-192-CM26</t>
+          <t>2799-216-CM26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -31934,12 +31934,12 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -31949,32 +31949,28 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K505" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.099.725-0</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>6477.85</v>
+        <v>3579.67</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2799-216-CM26</t>
+          <t>2799-207-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -32029,13 +32025,13 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>3579.67</v>
+        <v>39691.91</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2799-207-CM26</t>
+          <t>2594-192-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -32060,12 +32056,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -32075,22 +32071,26 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
-        </is>
-      </c>
-      <c r="K507" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>39691.91</v>
+        <v>6477.85</v>
       </c>
     </row>
     <row r="508">
@@ -32596,7 +32596,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>1057370-157-CM26</t>
+          <t>2594-223-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -32621,12 +32621,12 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -32636,28 +32636,32 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K516" t="inlineStr"/>
+          <t>76.378.846-6</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>5881.35</v>
+        <v>3310.25</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2594-223-CM26</t>
+          <t>1057370-157-CM26</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -32682,12 +32686,12 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -32697,32 +32701,28 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
-        </is>
-      </c>
-      <c r="K517" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr"/>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>3310.25</v>
+        <v>5881.35</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>1173463-27-CM26</t>
+          <t>3191-1071-CM26</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -32747,12 +32747,12 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>61.969.000-1</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -32762,12 +32762,12 @@
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS DE ILUMINACION ILUMINA LIMITADA</t>
         </is>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>77.883.900-8</t>
         </is>
       </c>
       <c r="K518" t="inlineStr"/>
@@ -32777,7 +32777,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>1014.01</v>
+        <v>12627.07</v>
       </c>
     </row>
     <row r="519">
@@ -32844,7 +32844,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>3191-1071-CM26</t>
+          <t>1173463-27-CM26</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -32869,12 +32869,12 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.969.000-1</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -32884,12 +32884,12 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS DE ILUMINACION ILUMINA LIMITADA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>77.883.900-8</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K520" t="inlineStr"/>
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>12627.07</v>
+        <v>1014.01</v>
       </c>
     </row>
     <row r="521">
@@ -33340,7 +33340,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>4077-24-CM26</t>
+          <t>2424-315-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -33365,12 +33365,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -33380,28 +33380,32 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
-        </is>
-      </c>
-      <c r="K528" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>7732.07</v>
+        <v>5413.06</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2424-315-CM26</t>
+          <t>1028-105-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -33426,12 +33430,12 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -33441,32 +33445,28 @@
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K529" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.590.760-7</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr"/>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>5413.06</v>
+        <v>58735.99</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>1028-105-CM26</t>
+          <t>2698-62-CM26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -33491,12 +33491,12 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -33506,28 +33506,32 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
-        </is>
-      </c>
-      <c r="K530" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>58735.99</v>
+        <v>2396.08</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2698-62-CM26</t>
+          <t>2698-63-CM26</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -33586,13 +33590,13 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>2396.08</v>
+        <v>7821.81</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2698-63-CM26</t>
+          <t>4077-24-CM26</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -33617,12 +33621,12 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -33632,32 +33636,28 @@
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K532" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr"/>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>7821.81</v>
+        <v>7732.07</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2755-85-CM26</t>
+          <t>2799-328-CM26</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -33682,12 +33682,12 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -33697,12 +33697,12 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>11.647.874-9</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K533" t="inlineStr"/>
@@ -33712,7 +33712,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>880.0599999999999</v>
+        <v>2790.8</v>
       </c>
     </row>
     <row r="534">
@@ -33779,7 +33779,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2799-328-CM26</t>
+          <t>2755-85-CM26</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -33804,12 +33804,12 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -33819,12 +33819,12 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>11.647.874-9</t>
         </is>
       </c>
       <c r="K535" t="inlineStr"/>
@@ -33834,7 +33834,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>2790.8</v>
+        <v>880.0599999999999</v>
       </c>
     </row>
     <row r="536">
@@ -33962,7 +33962,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>1171085-11-CM26</t>
+          <t>2698-68-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -33987,12 +33987,12 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -34002,28 +34002,32 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K538" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>2443.67</v>
+        <v>1747.73</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2687-52-CM26</t>
+          <t>1171085-11-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -34048,12 +34052,12 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -34063,32 +34067,28 @@
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K539" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr"/>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>2385.05</v>
+        <v>2443.67</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2698-68-CM26</t>
+          <t>2698-70-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -34128,12 +34128,12 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
@@ -34147,13 +34147,13 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>1747.73</v>
+        <v>10950.02</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2698-70-CM26</t>
+          <t>2687-52-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -34178,12 +34178,12 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -34193,12 +34193,12 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K541" t="inlineStr">
@@ -34212,7 +34212,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>10950.02</v>
+        <v>2385.05</v>
       </c>
     </row>
     <row r="542">
@@ -34661,7 +34661,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>3086-317-CM26</t>
+          <t>3086-316-CM26</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -34701,12 +34701,12 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K549" t="inlineStr"/>
@@ -34716,13 +34716,13 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>1951.87</v>
+        <v>1303.32</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>3086-321-CM26</t>
+          <t>3086-317-CM26</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -34762,32 +34762,28 @@
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K550" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr"/>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>4876.55</v>
+        <v>1951.87</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>1079516-312-CM26</t>
+          <t>3086-321-CM26</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -34812,12 +34808,12 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.102.005-8</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -34827,12 +34823,12 @@
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
@@ -34846,13 +34842,13 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>16060.43</v>
+        <v>4876.55</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>3086-316-CM26</t>
+          <t>1079516-312-CM26</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -34877,12 +34873,12 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>61.102.005-8</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -34892,22 +34888,26 @@
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>Francisco javier</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
-        </is>
-      </c>
-      <c r="K552" t="inlineStr"/>
+          <t>77.499.324-K</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1303.32</v>
+        <v>16060.43</v>
       </c>
     </row>
     <row r="553">
@@ -35035,7 +35035,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>3115-141-CM26</t>
+          <t>2737-203-CM26</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -35060,12 +35060,12 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>61.102.119-4</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -35075,26 +35075,22 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>GRUPO GMSE  NEGOCIOS SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>77.512.806-2</t>
-        </is>
-      </c>
-      <c r="K555" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr"/>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>7559.73</v>
+        <v>1892.6</v>
       </c>
     </row>
     <row r="556">
@@ -35165,7 +35161,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2737-203-CM26</t>
+          <t>2698-77-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -35190,12 +35186,12 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -35205,28 +35201,32 @@
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K557" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1892.6</v>
+        <v>909.6799999999999</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>4548-237-CM26</t>
+          <t>3115-141-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -35246,17 +35246,17 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>61.102.119-4</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -35266,28 +35266,32 @@
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t>GRUPO GMSE  NEGOCIOS SPA</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
-        </is>
-      </c>
-      <c r="K558" t="inlineStr"/>
+          <t>77.512.806-2</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>3360.15</v>
+        <v>7559.73</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2698-77-CM26</t>
+          <t>4548-237-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -35307,17 +35311,17 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -35327,26 +35331,22 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K559" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.590.760-7</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr"/>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>909.6799999999999</v>
+        <v>3360.15</v>
       </c>
     </row>
     <row r="560">
@@ -35413,7 +35413,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>1272271-26-CM26</t>
+          <t>3086-399-CM26</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -35438,12 +35438,12 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>61.004.122-1</t>
+          <t>61.102.005-8</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -35453,28 +35453,32 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>COMERCIAL MALMO S.A.</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>76.123.414-5</t>
-        </is>
-      </c>
-      <c r="K561" t="inlineStr"/>
+          <t>84.634.200-1</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>789.5599999999999</v>
+        <v>2931.18</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>3086-399-CM26</t>
+          <t>2799-406-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -35499,12 +35503,12 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>61.102.005-8</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -35514,32 +35518,28 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
-        </is>
-      </c>
-      <c r="K562" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.099.725-0</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr"/>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>2931.18</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2799-406-CM26</t>
+          <t>1272271-26-CM26</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -35564,12 +35564,12 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>61.004.122-1</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -35579,12 +35579,12 @@
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>COMERCIAL MALMO S.A.</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>76.123.414-5</t>
         </is>
       </c>
       <c r="K563" t="inlineStr"/>
@@ -35594,7 +35594,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>3120</v>
+        <v>789.5599999999999</v>
       </c>
     </row>
     <row r="564">
@@ -36474,7 +36474,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2698-96-CM26</t>
+          <t>2428-395-CM26</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -36499,12 +36499,12 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -36514,12 +36514,12 @@
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K578" t="inlineStr"/>
@@ -36529,13 +36529,13 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>3089.86</v>
+        <v>11847.82</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>1173462-8-CM26</t>
+          <t>2698-96-CM26</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -36560,12 +36560,12 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>61.969.100-8</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -36575,12 +36575,12 @@
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K579" t="inlineStr"/>
@@ -36590,13 +36590,13 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>6250.69</v>
+        <v>3089.86</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2428-395-CM26</t>
+          <t>1173462-8-CM26</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -36621,12 +36621,12 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.969.100-8</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -36636,12 +36636,12 @@
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K580" t="inlineStr"/>
@@ -36651,7 +36651,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>11847.82</v>
+        <v>6250.69</v>
       </c>
     </row>
     <row r="581">
@@ -36779,7 +36779,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>4964-29-CM26</t>
+          <t>1953-746-CM26</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -36804,12 +36804,12 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -36819,12 +36819,12 @@
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K583" t="inlineStr"/>
@@ -36834,13 +36834,13 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>1473.47</v>
+        <v>1106.04</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>1953-746-CM26</t>
+          <t>4964-29-CM26</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -36865,12 +36865,12 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -36880,12 +36880,12 @@
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K584" t="inlineStr"/>
@@ -36895,7 +36895,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>1106.04</v>
+        <v>1473.47</v>
       </c>
     </row>
     <row r="585">
@@ -37023,7 +37023,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>4844-39-CM26</t>
+          <t>539119-1454-CM26</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -37048,12 +37048,12 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -37063,12 +37063,12 @@
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K587" t="inlineStr">
@@ -37082,13 +37082,13 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>21759.01</v>
+        <v>7407.74</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2958-22-CM26</t>
+          <t>2950-214-CM26</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -37113,7 +37113,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>61.102.011-2</t>
+          <t>61.102.010-4</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -37128,12 +37128,12 @@
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  JMK  SPA</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>77.700.129-9</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K588" t="inlineStr">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>34203.34</v>
+        <v>1139.48</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>539119-1454-CM26</t>
+          <t>2958-22-CM26</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -37178,12 +37178,12 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.102.011-2</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -37193,12 +37193,12 @@
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA  JMK  SPA</t>
         </is>
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.700.129-9</t>
         </is>
       </c>
       <c r="K589" t="inlineStr">
@@ -37212,13 +37212,13 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>7407.74</v>
+        <v>34203.34</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2950-214-CM26</t>
+          <t>4844-39-CM26</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -37243,12 +37243,12 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>61.102.010-4</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -37277,7 +37277,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>1139.48</v>
+        <v>21759.01</v>
       </c>
     </row>
     <row r="591">
@@ -38100,7 +38100,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>707419-53-CM26</t>
+          <t>2696-44-CM26</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -38125,12 +38125,12 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -38140,28 +38140,32 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K604" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>15654.94</v>
+        <v>1526.39</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2696-44-CM26</t>
+          <t>707419-53-CM26</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -38186,12 +38190,12 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -38201,32 +38205,28 @@
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K605" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>1526.39</v>
+        <v>15654.94</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>3132-222-CM26</t>
+          <t>1953-931-CM26</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -38251,12 +38251,12 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>61.950.800-9</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -38266,17 +38266,17 @@
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA PETCH LIMITADA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>76.317.833-1</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -38285,13 +38285,13 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>3791.86</v>
+        <v>2793.93</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>1953-931-CM26</t>
+          <t>3132-222-CM26</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -38316,12 +38316,12 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>61.950.800-9</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -38331,17 +38331,17 @@
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>COMERCIALIZADORA PETCH LIMITADA</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>76.317.833-1</t>
         </is>
       </c>
       <c r="K607" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
@@ -38350,13 +38350,13 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>2793.93</v>
+        <v>3791.86</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>1173462-10-CM26</t>
+          <t>3047-230-CM26</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -38381,12 +38381,12 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>61.969.100-8</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -38396,28 +38396,32 @@
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
-        </is>
-      </c>
-      <c r="K608" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>827.4299999999999</v>
+        <v>1260.59</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>3047-230-CM26</t>
+          <t>3882-188-CM26</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -38442,12 +38446,12 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -38476,13 +38480,13 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>1260.59</v>
+        <v>9342.48</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>3882-188-CM26</t>
+          <t>1173462-10-CM26</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -38507,12 +38511,12 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>61.969.100-8</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -38522,26 +38526,22 @@
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K610" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr"/>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>9342.48</v>
+        <v>827.4299999999999</v>
       </c>
     </row>
     <row r="611">
@@ -38795,7 +38795,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>1953-979-CM26</t>
+          <t>2698-138-CM26</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -38820,12 +38820,12 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -38835,12 +38835,12 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K615" t="inlineStr"/>
@@ -38850,13 +38850,13 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>811.77</v>
+        <v>8478.52</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2698-138-CM26</t>
+          <t>1953-979-CM26</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -38881,12 +38881,12 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -38896,12 +38896,12 @@
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K616" t="inlineStr"/>
@@ -38911,7 +38911,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>8478.52</v>
+        <v>811.77</v>
       </c>
     </row>
     <row r="617">
@@ -39222,7 +39222,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2428-561-CM26</t>
+          <t>4964-53-CM26</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -39247,12 +39247,12 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -39262,32 +39262,28 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K622" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr"/>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>8870.02</v>
+        <v>1182.61</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>4964-53-CM26</t>
+          <t>2428-561-CM26</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -39312,12 +39308,12 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -39327,22 +39323,26 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K623" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>1182.61</v>
+        <v>8870.02</v>
       </c>
     </row>
     <row r="624">
@@ -39775,7 +39775,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>1099899-107-CM26</t>
+          <t>5509-35-CM26</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -39795,17 +39795,17 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -39815,26 +39815,22 @@
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K631" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr"/>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>1065.7</v>
+        <v>2142.45</v>
       </c>
     </row>
     <row r="632">
@@ -39901,7 +39897,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>5509-35-CM26</t>
+          <t>1099899-107-CM26</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -39921,17 +39917,17 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -39941,22 +39937,26 @@
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
-        </is>
-      </c>
-      <c r="K633" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>2142.45</v>
+        <v>1065.7</v>
       </c>
     </row>
     <row r="634">
@@ -40523,7 +40523,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>4964-60-CM26</t>
+          <t>1231-64-CM26</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -40548,12 +40548,12 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>60.804.008-0</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -40563,12 +40563,12 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K643" t="inlineStr"/>
@@ -40578,13 +40578,13 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>1070.65</v>
+        <v>786.2</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>1943-205-CM26</t>
+          <t>2920-121-CM26</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -40604,17 +40604,17 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.252.300-8</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -40624,28 +40624,32 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguridad Industrial SPA </t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>76.756.768-5</t>
-        </is>
-      </c>
-      <c r="K644" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>5061.23</v>
+        <v>1394.24</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>836-105-CM26</t>
+          <t>2176-315-CM26</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -40665,17 +40669,17 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -40685,12 +40689,12 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K645" t="inlineStr"/>
@@ -40700,13 +40704,13 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>3064</v>
+        <v>3903.64</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2920-121-CM26</t>
+          <t>2698-161-CM26</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -40726,17 +40730,17 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -40746,17 +40750,17 @@
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -40765,13 +40769,13 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>1394.24</v>
+        <v>8648.74</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2176-315-CM26</t>
+          <t>4964-60-CM26</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -40791,17 +40795,17 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -40811,12 +40815,12 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K647" t="inlineStr"/>
@@ -40826,13 +40830,13 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>3903.64</v>
+        <v>1070.65</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2698-161-CM26</t>
+          <t>836-105-CM26</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -40857,12 +40861,12 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -40872,32 +40876,28 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K648" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr"/>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>8648.74</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>1231-64-CM26</t>
+          <t>1943-205-CM26</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -40922,12 +40922,12 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>60.804.008-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -40937,12 +40937,12 @@
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.756.768-5</t>
         </is>
       </c>
       <c r="K649" t="inlineStr"/>
@@ -40952,7 +40952,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>786.2</v>
+        <v>5061.23</v>
       </c>
     </row>
     <row r="650">
@@ -41332,7 +41332,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>3223-118-CM26</t>
+          <t>1704-3640-CM26</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -41352,17 +41352,17 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>61.102.019-8</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -41372,12 +41372,12 @@
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K656" t="inlineStr"/>
@@ -41387,13 +41387,13 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>1526.9</v>
+        <v>782.1</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>1704-3640-CM26</t>
+          <t>3223-118-CM26</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -41413,17 +41413,17 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.102.019-8</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -41433,12 +41433,12 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.724.952-7</t>
         </is>
       </c>
       <c r="K657" t="inlineStr"/>
@@ -41448,13 +41448,13 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>782.1</v>
+        <v>1526.9</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>594807-45-CM26</t>
+          <t>4548-429-CM26</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -41474,17 +41474,17 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>61.979.670-5</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -41494,17 +41494,17 @@
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>GRUPO GMSE  NEGOCIOS SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>77.512.806-2</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L658" t="inlineStr">
@@ -41513,13 +41513,13 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>14806.36</v>
+        <v>12421.16</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2698-172-CM26</t>
+          <t>594807-45-CM26</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -41544,12 +41544,12 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.979.670-5</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -41559,17 +41559,17 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>GRUPO GMSE  NEGOCIOS SPA</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.512.806-2</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L659" t="inlineStr">
@@ -41578,13 +41578,13 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>5077.72</v>
+        <v>14806.36</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>4548-429-CM26</t>
+          <t>2698-172-CM26</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -41604,17 +41604,17 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -41624,12 +41624,12 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
@@ -41643,7 +41643,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>12421.16</v>
+        <v>5077.72</v>
       </c>
     </row>
     <row r="661">
@@ -41958,7 +41958,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2428-766-CM26</t>
+          <t>760-231-CM26</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -41978,17 +41978,17 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -41998,28 +41998,32 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K666" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>8008.48</v>
+        <v>1405.18</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>760-231-CM26</t>
+          <t>4077-106-CM26</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -42039,17 +42043,17 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -42059,12 +42063,12 @@
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
@@ -42078,13 +42082,13 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>1405.18</v>
+        <v>9678.74</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>4077-106-CM26</t>
+          <t>2428-766-CM26</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -42109,12 +42113,12 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -42124,32 +42128,28 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K668" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr"/>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>9678.74</v>
+        <v>8008.48</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>4844-54-CM26</t>
+          <t>3882-281-CM26</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -42174,12 +42174,12 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -42189,12 +42189,12 @@
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
@@ -42208,7 +42208,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>18714.75</v>
+        <v>2100.78</v>
       </c>
     </row>
     <row r="670">
@@ -42275,7 +42275,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>3882-281-CM26</t>
+          <t>4844-54-CM26</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -42300,12 +42300,12 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -42315,12 +42315,12 @@
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
@@ -42334,7 +42334,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>2100.78</v>
+        <v>18714.75</v>
       </c>
     </row>
     <row r="672">
@@ -42909,7 +42909,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>3191-3810-CM26</t>
+          <t>568658-1133-CM26</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -42934,12 +42934,12 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -42949,17 +42949,17 @@
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L681" t="inlineStr">
@@ -42968,13 +42968,13 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>843.53</v>
+        <v>8293.299999999999</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>568658-1133-CM26</t>
+          <t>3191-3810-CM26</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -42999,12 +42999,12 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -43014,17 +43014,17 @@
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L682" t="inlineStr">
@@ -43033,7 +43033,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>8293.299999999999</v>
+        <v>843.53</v>
       </c>
     </row>
     <row r="683">
@@ -43478,7 +43478,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>3275-7159-CM26</t>
+          <t>1028-233-CM26</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -43503,12 +43503,12 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -43518,12 +43518,12 @@
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K690" t="inlineStr"/>
@@ -43533,13 +43533,13 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>1889.62</v>
+        <v>12649.94</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>2958-50-CM26</t>
+          <t>3275-7159-CM26</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -43564,12 +43564,12 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>61.102.011-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -43579,32 +43579,28 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K691" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr"/>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>40489.72</v>
+        <v>1889.62</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>1028-233-CM26</t>
+          <t>2958-50-CM26</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -43629,12 +43625,12 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.102.011-2</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -43644,28 +43640,32 @@
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
-        </is>
-      </c>
-      <c r="K692" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>12649.94</v>
+        <v>40489.72</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>3275-7161-CM26</t>
+          <t>1028-234-CM26</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -43690,12 +43690,12 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -43705,12 +43705,12 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>99.590.760-7</t>
         </is>
       </c>
       <c r="K693" t="inlineStr"/>
@@ -43720,13 +43720,13 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>1850.6</v>
+        <v>31190.2</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>1028-234-CM26</t>
+          <t>3275-7161-CM26</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -43751,12 +43751,12 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -43766,12 +43766,12 @@
       </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K694" t="inlineStr"/>
@@ -43781,7 +43781,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>31190.2</v>
+        <v>1850.6</v>
       </c>
     </row>
     <row r="695">
@@ -43852,7 +43852,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2945-615-CM26</t>
+          <t>707419-98-CM26</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -43877,12 +43877,12 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>61.102.004-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -43892,17 +43892,17 @@
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA PETCH LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>76.317.833-1</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L696" t="inlineStr">
@@ -43911,13 +43911,13 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>48662.75</v>
+        <v>7396.1</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>707419-98-CM26</t>
+          <t>2945-615-CM26</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -43942,12 +43942,12 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.102.004-K</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -43957,17 +43957,17 @@
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA PETCH LIMITADA</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.317.833-1</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
@@ -43976,13 +43976,13 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>7396.1</v>
+        <v>48662.75</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>3223-134-CM26</t>
+          <t>1134432-555-CM26</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -44007,12 +44007,12 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>61.102.019-8</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -44022,28 +44022,32 @@
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>CRISTIAN</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>77.054.796-2</t>
-        </is>
-      </c>
-      <c r="K698" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>1701.63</v>
+        <v>5497.67</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2427-684-CM26</t>
+          <t>3223-134-CM26</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -44063,17 +44067,17 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>61.102.019-8</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -44083,32 +44087,28 @@
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>CRISTIAN</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K699" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.054.796-2</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr"/>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>2216.29</v>
+        <v>1701.63</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>3515-357-CM26</t>
+          <t>2427-684-CM26</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -44133,12 +44133,12 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -44148,17 +44148,17 @@
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L700" t="inlineStr">
@@ -44167,13 +44167,13 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>16455.63</v>
+        <v>2216.29</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>1134432-555-CM26</t>
+          <t>3515-357-CM26</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -44193,17 +44193,17 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -44213,17 +44213,17 @@
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K701" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L701" t="inlineStr">
@@ -44232,13 +44232,13 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>5497.67</v>
+        <v>16455.63</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>3544-183-CM26</t>
+          <t>3544-182-CM26</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -44278,28 +44278,32 @@
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K702" t="inlineStr"/>
+          <t>84.634.200-1</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>995.39</v>
+        <v>4955.81</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>3232-522-CM26</t>
+          <t>3544-183-CM26</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -44324,12 +44328,12 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -44339,12 +44343,12 @@
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K703" t="inlineStr"/>
@@ -44354,13 +44358,13 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>2899.38</v>
+        <v>995.39</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>3544-182-CM26</t>
+          <t>3232-522-CM26</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -44385,12 +44389,12 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -44400,26 +44404,22 @@
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
-        </is>
-      </c>
-      <c r="K704" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr"/>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>4955.81</v>
+        <v>2899.38</v>
       </c>
     </row>
     <row r="705">
@@ -45047,7 +45047,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>1285502-22-CM26</t>
+          <t>1431841-925-CM26</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -45072,12 +45072,12 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -45087,12 +45087,12 @@
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
@@ -45106,13 +45106,13 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>2186.36</v>
+        <v>898.95</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>3232-527-CM26</t>
+          <t>1285502-22-CM26</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -45137,12 +45137,12 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -45152,17 +45152,17 @@
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>NELCO SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>77.094.046-K</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L716" t="inlineStr">
@@ -45171,13 +45171,13 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>34735.7</v>
+        <v>2186.36</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>1431841-925-CM26</t>
+          <t>3232-527-CM26</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -45202,12 +45202,12 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -45217,17 +45217,17 @@
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>NELCO SPA</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.094.046-K</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
@@ -45236,7 +45236,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>898.95</v>
+        <v>34735.7</v>
       </c>
     </row>
     <row r="718">
@@ -45433,7 +45433,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>1134432-588-CM26</t>
+          <t>2755-343-CM26</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -45453,17 +45453,17 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -45473,12 +45473,12 @@
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>Comercial Disaferco Limitada</t>
+          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>76.127.832-0</t>
+          <t>11.647.874-9</t>
         </is>
       </c>
       <c r="K721" t="inlineStr"/>
@@ -45488,13 +45488,13 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>856.38</v>
+        <v>3351.12</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>2755-343-CM26</t>
+          <t>1134432-588-CM26</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -45514,17 +45514,17 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -45534,12 +45534,12 @@
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
+          <t>Comercial Disaferco Limitada</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>11.647.874-9</t>
+          <t>76.127.832-0</t>
         </is>
       </c>
       <c r="K722" t="inlineStr"/>
@@ -45549,7 +45549,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>3351.12</v>
+        <v>856.38</v>
       </c>
     </row>
     <row r="723">
@@ -45990,7 +45990,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>2698-203-CM26</t>
+          <t>4548-528-CM26</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -46015,12 +46015,12 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -46030,12 +46030,12 @@
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>99.590.760-7</t>
         </is>
       </c>
       <c r="K730" t="inlineStr"/>
@@ -46045,7 +46045,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>5408.45</v>
+        <v>2286.53</v>
       </c>
     </row>
     <row r="731">
@@ -46112,7 +46112,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>4548-528-CM26</t>
+          <t>2698-203-CM26</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -46137,12 +46137,12 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -46152,12 +46152,12 @@
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K732" t="inlineStr"/>
@@ -46167,13 +46167,13 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>2286.53</v>
+        <v>5408.45</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>586-395-CM26</t>
+          <t>3544-207-CM26</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -46198,12 +46198,12 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -46213,12 +46213,12 @@
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K733" t="inlineStr"/>
@@ -46228,13 +46228,13 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>10708.99</v>
+        <v>4865.42</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>3544-207-CM26</t>
+          <t>586-395-CM26</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -46259,12 +46259,12 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -46274,12 +46274,12 @@
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K734" t="inlineStr"/>
@@ -46289,13 +46289,13 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>4865.42</v>
+        <v>10708.99</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>2487-35-CM26</t>
+          <t>1943-313-CM26</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -46315,17 +46315,17 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -46335,12 +46335,12 @@
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
+          <t>76.756.768-5</t>
         </is>
       </c>
       <c r="K735" t="inlineStr"/>
@@ -46350,13 +46350,13 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>17291.24</v>
+        <v>1736.29</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>3544-213-CM26</t>
+          <t>2487-35-CM26</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -46381,12 +46381,12 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -46396,12 +46396,12 @@
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>99.590.760-7</t>
         </is>
       </c>
       <c r="K736" t="inlineStr"/>
@@ -46411,13 +46411,13 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>32690.15</v>
+        <v>17291.24</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>1943-313-CM26</t>
+          <t>3544-213-CM26</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -46437,17 +46437,17 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -46457,12 +46457,12 @@
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguridad Industrial SPA </t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>76.756.768-5</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K737" t="inlineStr"/>
@@ -46472,13 +46472,13 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>1736.29</v>
+        <v>32690.15</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>1704-4789-CM26</t>
+          <t>2799-868-CM26</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -46503,12 +46503,12 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -46518,12 +46518,12 @@
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K738" t="inlineStr"/>
@@ -46533,13 +46533,13 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>850.1799999999999</v>
+        <v>776.2</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2799-876-CM26</t>
+          <t>2171-421-CM26</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -46564,12 +46564,12 @@
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>61.606.611-0</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>HOSPITAL SAN AGUSTIN DE LA LIGUA</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -46579,28 +46579,32 @@
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
-        </is>
-      </c>
-      <c r="K739" t="inlineStr"/>
+          <t>77.819.582-8</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>2806</v>
+        <v>2791.07</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2799-868-CM26</t>
+          <t>1704-4789-CM26</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -46625,12 +46629,12 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -46640,12 +46644,12 @@
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K740" t="inlineStr"/>
@@ -46655,13 +46659,13 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>776.2</v>
+        <v>850.1799999999999</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2171-421-CM26</t>
+          <t>2799-876-CM26</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -46686,12 +46690,12 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>61.606.611-0</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>HOSPITAL SAN AGUSTIN DE LA LIGUA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -46701,26 +46705,22 @@
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
-        </is>
-      </c>
-      <c r="K741" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.851.313-9</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr"/>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>2791.07</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="742">
@@ -46974,7 +46974,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2799-905-CM26</t>
+          <t>576181-162-CM26</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -46999,12 +46999,12 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>61.979.760-4</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -47014,12 +47014,12 @@
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
+          <t>76.724.952-7</t>
         </is>
       </c>
       <c r="K746" t="inlineStr"/>
@@ -47029,13 +47029,13 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>2037.98</v>
+        <v>3286.22</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>576181-162-CM26</t>
+          <t>2799-905-CM26</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -47055,17 +47055,17 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>61.979.760-4</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -47075,12 +47075,12 @@
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
+          <t>76.851.313-9</t>
         </is>
       </c>
       <c r="K747" t="inlineStr"/>
@@ -47090,7 +47090,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>3286.22</v>
+        <v>2037.98</v>
       </c>
     </row>
     <row r="748">
@@ -47226,7 +47226,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2427-820-CM26</t>
+          <t>377-406-CM26</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -47246,17 +47246,17 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -47266,12 +47266,12 @@
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K750" t="inlineStr"/>
@@ -47281,13 +47281,13 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>894.3099999999999</v>
+        <v>5539.57</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>377-406-CM26</t>
+          <t>2427-820-CM26</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -47307,17 +47307,17 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -47327,12 +47327,12 @@
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K751" t="inlineStr"/>
@@ -47342,7 +47342,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>5539.57</v>
+        <v>894.3099999999999</v>
       </c>
     </row>
     <row r="752">
@@ -47982,7 +47982,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>3781-186-CM26</t>
+          <t>2698-222-CM26</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -48002,17 +48002,17 @@
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>61.102.008-2</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -48022,17 +48022,17 @@
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA PETCH LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>76.317.833-1</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L762" t="inlineStr">
@@ -48041,13 +48041,13 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>7897.95</v>
+        <v>6788.68</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>1953-1777-CM26</t>
+          <t>3781-186-CM26</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -48072,12 +48072,12 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>61.102.008-2</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
@@ -48087,17 +48087,17 @@
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA PETCH LIMITADA</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.317.833-1</t>
         </is>
       </c>
       <c r="K763" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L763" t="inlineStr">
@@ -48106,13 +48106,13 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>979.1799999999999</v>
+        <v>7897.95</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2698-222-CM26</t>
+          <t>1953-1777-CM26</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -48132,17 +48132,17 @@
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
@@ -48152,12 +48152,12 @@
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
@@ -48171,13 +48171,13 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>6788.68</v>
+        <v>979.1799999999999</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>4819-117-CM26</t>
+          <t>1171085-44-CM26</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -48197,17 +48197,17 @@
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
@@ -48217,12 +48217,12 @@
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K765" t="inlineStr">
@@ -48236,13 +48236,13 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>914.34</v>
+        <v>1018.37</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>1171085-44-CM26</t>
+          <t>4819-117-CM26</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -48262,17 +48262,17 @@
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
@@ -48282,12 +48282,12 @@
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K766" t="inlineStr">
@@ -48301,7 +48301,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>1018.37</v>
+        <v>914.34</v>
       </c>
     </row>
     <row r="767">
@@ -49201,7 +49201,7 @@
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F781" t="inlineStr">
@@ -49303,7 +49303,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>760-341-CM26</t>
+          <t>1134432-711-CM26</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -49328,12 +49328,12 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
@@ -49343,28 +49343,32 @@
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K783" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L783" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>801.72</v>
+        <v>13036.75</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>1134432-711-CM26</t>
+          <t>760-341-CM26</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -49389,12 +49393,12 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -49404,26 +49408,22 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K784" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr"/>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>13036.75</v>
+        <v>801.72</v>
       </c>
     </row>
     <row r="785">
@@ -49620,7 +49620,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>836-159-CM26</t>
+          <t>529318-180-CM26</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -49645,12 +49645,12 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>61.102.008-2</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
@@ -49660,28 +49660,32 @@
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>COMERCIALIZADORA PETCH LIMITADA</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
-        </is>
-      </c>
-      <c r="K788" t="inlineStr"/>
+          <t>76.317.833-1</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L788" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>2202.27</v>
+        <v>7637.58</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2755-452-CM26</t>
+          <t>836-159-CM26</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -49706,12 +49710,12 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -49721,12 +49725,12 @@
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>11.647.874-9</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K789" t="inlineStr"/>
@@ -49736,13 +49740,13 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>6084.81</v>
+        <v>2202.27</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>799512-1136-CM26</t>
+          <t>2755-452-CM26</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -49767,12 +49771,12 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
@@ -49782,12 +49786,12 @@
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
+          <t>11.647.874-9</t>
         </is>
       </c>
       <c r="K790" t="inlineStr"/>
@@ -49797,13 +49801,13 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>1902.33</v>
+        <v>6084.81</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>3223-171-CM26</t>
+          <t>799512-1136-CM26</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -49828,12 +49832,12 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>61.102.019-8</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -49843,32 +49847,28 @@
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K791" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.724.952-7</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr"/>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>4869.65</v>
+        <v>1902.33</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>1173463-126-CM26</t>
+          <t>3223-171-CM26</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -49893,12 +49893,12 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>61.969.000-1</t>
+          <t>61.102.019-8</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -49908,28 +49908,32 @@
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
-        </is>
-      </c>
-      <c r="K792" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>3499.6</v>
+        <v>4869.65</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>529318-180-CM26</t>
+          <t>1173463-126-CM26</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -49954,12 +49958,12 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>61.102.008-2</t>
+          <t>61.969.000-1</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
@@ -49969,26 +49973,22 @@
       </c>
       <c r="I793" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA PETCH LIMITADA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>76.317.833-1</t>
-        </is>
-      </c>
-      <c r="K793" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr"/>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>7637.58</v>
+        <v>3499.6</v>
       </c>
     </row>
     <row r="794">
@@ -50303,7 +50303,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>1134432-701-CM26</t>
+          <t>1134432-714-CM26</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -50343,90 +50343,151 @@
       </c>
       <c r="I799" t="inlineStr">
         <is>
-          <t>OSCAR ARMANDO ZÚÑIGA VALENZUELA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>10.020.938-1</t>
-        </is>
-      </c>
-      <c r="K799" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.397.758-7</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr"/>
       <c r="L799" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>36479.66</v>
+        <v>1254.92</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
+          <t>1134432-701-CM26</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>OSCAR ARMANDO ZÚÑIGA VALENZUELA</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>10.020.938-1</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M800" s="2" t="n">
+        <v>36479.66</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
           <t>3115-217-CM26</t>
         </is>
       </c>
-      <c r="B800" t="inlineStr">
-        <is>
-          <t>2239-9-LR23</t>
-        </is>
-      </c>
-      <c r="C800" t="inlineStr">
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D800" t="inlineStr">
+      <c r="D801" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="E800" t="inlineStr">
+      <c r="E801" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F800" t="inlineStr">
+      <c r="F801" t="inlineStr">
         <is>
           <t>61.102.119-4</t>
         </is>
       </c>
-      <c r="G800" t="inlineStr">
+      <c r="G801" t="inlineStr">
         <is>
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H800" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I800" t="inlineStr">
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
         <is>
           <t>GRUPO GMSE  NEGOCIOS SPA</t>
         </is>
       </c>
-      <c r="J800" t="inlineStr">
+      <c r="J801" t="inlineStr">
         <is>
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="L800" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M800" s="2" t="n">
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M801" s="2" t="n">
         <v>3605.25</v>
       </c>
     </row>
